--- a/output/pdf_financials_xlsx/LCFS.xlsx
+++ b/output/pdf_financials_xlsx/LCFS.xlsx
@@ -11310,7 +11310,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E191" s="5" t="n">

--- a/output/pdf_financials_xlsx/LCFS.xlsx
+++ b/output/pdf_financials_xlsx/LCFS.xlsx
@@ -1110,12 +1110,10 @@
         <v>-41.019</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-357.846</v>
-      </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-357.9</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="24">
@@ -2862,12 +2860,10 @@
         <v>-41.019</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-357.846</v>
-      </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-357.9</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="100">
@@ -3097,13 +3093,13 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.766</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>7.898</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
@@ -12974,7 +12970,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -13442,7 +13442,11 @@
           <t>Deferred income tax recovery 14</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -14960,7 +14964,11 @@
           <t>Accretion 16</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -15153,7 +15161,11 @@
           <t>Deferred income tax expense (recovery) 12</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -15971,7 +15983,11 @@
           <t>Accretion 17</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E306" s="5" t="n">
         <v>0.766</v>
       </c>
@@ -16131,7 +16147,11 @@
           <t>Deferred income tax expense 13</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E310" s="5" t="n">
         <v>1.234</v>
       </c>
@@ -16801,7 +16821,11 @@
           <t>Accretion 13</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E326" s="5" t="n">
         <v>0.766</v>
       </c>
@@ -16924,7 +16948,11 @@
           <t>Deferred income tax expense 10</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E329" s="5" t="n">
         <v>1.234</v>
       </c>
